--- a/out/Attention-mamba2_repeat_4_000006.xlsx
+++ b/out/Attention-mamba2_repeat_4_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001989762606696458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2560979469865662</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.512680554479097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05914354241208649</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1967554283138102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1967554283138102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1965487919540231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6348315863712745</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.467476062762909</v>
+        <v>-7.49195503629744e-06</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1214678088929625</v>
+        <v>-0.005815864238860101</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.074653806082069</v>
+        <v>-0.005823356193896383</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.212762604587615</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.378770624817541</v>
+        <v>-0.005831530705007143</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1165163065681132</v>
+        <v>0.0002048618514369727</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.398857721817736</v>
+        <v>-0.004623343201367068</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04812312828442799</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.378465049385182</v>
+        <v>-0.006635027406380395</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05995679777368613</v>
+        <v>0.006680975705700599</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.450264575555993</v>
+        <v>0.007751243551780586</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03610173702120535</v>
+        <v>0.00456499504850022</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.462470765836948</v>
+        <v>0.01019448263846314</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02744702530298617</v>
+        <v>0.004163237700556995</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.481248268482755</v>
+        <v>0.01395410596934543</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01213878067296011</v>
+        <v>0.001761718820563854</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.462243845257878</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.478055499241708</v>
+        <v>0.01331021800604113</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009632371338442582</v>
+        <v>0.001593552918993004</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.462243845257878</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.485176373792796</v>
+        <v>0.01473374977943383</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00477282730291264</v>
+        <v>0.0007863362758661484</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.462243845257878</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.485086080677008</v>
+        <v>0.01471165066235361</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002773286712076212</v>
+        <v>0.0004675096739788983</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.462243845257878</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.485857711472164</v>
+        <v>0.01486230338965252</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00138559795641092</v>
+        <v>0.0002324917733087656</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.485850980083836</v>
+        <v>0.01485695566312631</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006820409108092269</v>
+        <v>0.0001120873626584866</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.485828588333292</v>
+        <v>0.01484846275925147</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003921806805704257</v>
+        <v>6.465579210174811e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.4859338870932</v>
+        <v>0.01486561439602845</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001289182068383145</v>
+        <v>1.655970408370411e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.986393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.485795877254044</v>
+        <v>0.01483401242819708</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.23737344181313e-05</v>
+        <v>5.862778241646865e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.986393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.485791622759251</v>
+        <v>0.01482916152923857</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.169294195162759e-05</v>
+        <v>1.032604069335822e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8622438452578782</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.48579259614381</v>
+        <v>0.01482535620615038</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>-3.065147660033304e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.986393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.485786433716788</v>
+        <v>0.01482012491056579</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.526127361367024e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.386393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.485785736571384</v>
+        <v>0.01481620062421483</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.462243845257878</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.485779401710837</v>
+        <v>0.01481586852089164</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.386393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.485775159100683</v>
+        <v>0.01481624905594939</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.462243845257878</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.485775387421718</v>
+        <v>0.01481647737698408</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386393030374176</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.485775477366368</v>
+        <v>0.01481656732163415</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.485774619432783</v>
+        <v>0.01481570938804932</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.485774847753818</v>
+        <v>0.0148159377090839</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.485774052089606</v>
+        <v>0.01481514204487216</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.485774114358979</v>
+        <v>0.01481520431424526</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.485774142034256</v>
+        <v>0.01481523198952223</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.485774294248279</v>
+        <v>0.01481538420354528</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.485773948307317</v>
+        <v>0.01481503826258366</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.485774024414329</v>
+        <v>0.01481511436959531</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.48577419046599</v>
+        <v>0.0148152804212569</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.386393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.48577455024459</v>
+        <v>0.01481564019985695</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.485774571001048</v>
+        <v>0.01481566095631465</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.485774674783336</v>
+        <v>0.01481576473860315</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.485774903104371</v>
+        <v>0.01481599305963784</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.485774778565625</v>
+        <v>0.01481586852089164</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.485774806240902</v>
+        <v>0.0148158961961685</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.485774861591456</v>
+        <v>0.01481595154672244</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.485775124506587</v>
+        <v>0.01481621446185326</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.485775041480756</v>
+        <v>0.01481613143602246</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.485774833916179</v>
+        <v>0.01481592387144547</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.485774847753818</v>
+        <v>0.0148159377090839</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.485774986130202</v>
+        <v>0.01481607608546864</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.485774702458614</v>
+        <v>0.01481579241388012</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.485774529488133</v>
+        <v>0.01481561944339925</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.485774425705845</v>
+        <v>0.01481551566111075</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.485774571001048</v>
+        <v>0.01481566095631465</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.485774813159721</v>
+        <v>0.01481590311498777</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.485774640189241</v>
+        <v>0.01481573014450702</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.485774342680014</v>
+        <v>0.01481543263527995</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.485774328842375</v>
+        <v>0.01481541879764153</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.485773962144955</v>
+        <v>0.01481505210022221</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.485773962144955</v>
+        <v>0.01481505210022221</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.986393030374176</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.485773899875583</v>
+        <v>0.01481498983084911</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.485773796093294</v>
+        <v>0.01481488604856061</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8622438452578782</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.485773623122813</v>
+        <v>0.01481471307807975</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.485773671554548</v>
+        <v>0.01481476150981442</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.462243845257878</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.485773311775948</v>
+        <v>0.01481440173121425</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.485773270263033</v>
+        <v>0.01481436021829886</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.485773325613586</v>
+        <v>0.0148144155688528</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.48577338096414</v>
+        <v>0.01481447091940662</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.485773422477056</v>
+        <v>0.01481451243232202</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.485773152643105</v>
+        <v>0.01481424259837193</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.485773207993659</v>
+        <v>0.01481429794892576</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.485773353288863</v>
+        <v>0.01481444324412965</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.485773318694767</v>
+        <v>0.01481440865003352</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.485773304857129</v>
+        <v>0.0148143948123951</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.485773394801779</v>
+        <v>0.01481448475704505</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.485773713067463</v>
+        <v>0.01481480302272981</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.485773533178163</v>
+        <v>0.01481462313342979</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8622438452578782</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.485773574691079</v>
+        <v>0.01481466464634519</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.48577338788296</v>
+        <v>0.0148144778382259</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.485773457071152</v>
+        <v>0.01481454702641815</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.485773256425394</v>
+        <v>0.01481434638066043</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.48577329793831</v>
+        <v>0.01481438789357583</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>-4.309040656955487e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.462243845257878</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.485773325613586</v>
+        <v>0.0148144155688528</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000006.xlsx
+++ b/out/Attention-mamba2_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001989762606696458</v>
+        <v>-0.0001868916883917991</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2560979469865662</v>
+        <v>0.2405439506599493</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.512680554479097</v>
+        <v>0.4815435480673604</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05914354241208649</v>
+        <v>-0.05555158254951009</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1967554283138102</v>
+        <v>0.1848054764220475</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1967554283138102</v>
+        <v>0.1848054764220475</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1965487919540231</v>
+        <v>0.1846764270315873</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6348315863712745</v>
+        <v>0.3964676369177444</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121083</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.467476062762909</v>
+        <v>0.9784011605977389</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1214678088929625</v>
+        <v>0.07585961506419546</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.074653806082069</v>
+        <v>0.7330741868823708</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.212762604587615</v>
+        <v>0.1328753101658987</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.378770624817541</v>
+        <v>0.9230023779499026</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1165163065681132</v>
+        <v>0.07276711699654888</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.398857721817736</v>
+        <v>0.9355472482495468</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04812312828442799</v>
+        <v>0.03005387904801072</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.378465049385182</v>
+        <v>0.9228115237015914</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05995679777368613</v>
+        <v>0.03744455424368934</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.450264575555993</v>
+        <v>0.9676523856496301</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03610173702120535</v>
+        <v>0.022546458456379</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.462470765836948</v>
+        <v>0.9752755391208245</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02744702530298617</v>
+        <v>0.01714136955187149</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.481248268482755</v>
+        <v>0.9870028011655845</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01213878067296011</v>
+        <v>0.007579101736862406</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.478055499241708</v>
+        <v>0.9850068797781947</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009632371338442582</v>
+        <v>0.006012997386423449</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.485176373792796</v>
+        <v>0.9894525224497505</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00477282730291264</v>
+        <v>0.002979265954122921</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.485086080677008</v>
+        <v>0.9893942399526222</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002773286712076212</v>
+        <v>0.001731792845140836</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.485857711472164</v>
+        <v>0.9898744806679504</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00138559795641092</v>
+        <v>0.0008619418221976032</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386393030374176</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.485850980083836</v>
+        <v>0.9898684012668587</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006820409108092269</v>
+        <v>0.0004233225761948737</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.485828588333292</v>
+        <v>0.9898525241169843</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003921806805704257</v>
+        <v>0.0002453239583427053</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.4859338870932</v>
+        <v>0.9899167479819124</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001289182068383145</v>
+        <v>7.75828942169606e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.485795877254044</v>
+        <v>0.9898286182366882</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.23737344181313e-05</v>
+        <v>3.767003179814982e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.485791622759251</v>
+        <v>0.9898240903899865</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.169294195162759e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8622438452578782</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.48579259614381</v>
+        <v>0.9898228750664795</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>6.850902234816308e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.485786433716788</v>
+        <v>0.9898170991236148</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.386393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.485785736571384</v>
+        <v>0.9898147902188129</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.462243845257878</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.485779401710837</v>
+        <v>0.9898087906852162</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.386393030374176</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.485775159100683</v>
+        <v>0.9898045480750622</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.462243845257878</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.485775387421718</v>
+        <v>0.9898047763960969</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386393030374176</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.485775477366368</v>
+        <v>0.9898048663407468</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.462243845257878</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.485774619432783</v>
+        <v>0.989804008407162</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.3452667921121083</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.485774847753818</v>
+        <v>0.9898042367281967</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.485774052089606</v>
+        <v>0.989803441063985</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.485774114358979</v>
+        <v>0.9898035033333581</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.485774142034256</v>
+        <v>0.9898035310086349</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386393030374176</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.485774294248279</v>
+        <v>0.9898036832226582</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323613</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.485773948307317</v>
+        <v>0.9898033372816964</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.485774024414329</v>
+        <v>0.9898034133887081</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.462243845257878</v>
+        <v>0.3058502080323614</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.48577419046599</v>
+        <v>0.9898035794403698</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.386393030374176</v>
+        <v>-0.3452667921121082</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.48577455024459</v>
+        <v>0.9898039392189698</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.986393030374176</v>
+        <v>-1.196383792256578</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.485774571001048</v>
+        <v>0.9898039599754275</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.986393030374176</v>
+        <v>-0.5452667921121084</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.485774674783336</v>
+        <v>0.989804063757716</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.485774903104371</v>
+        <v>0.9898042920787506</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.485774778565625</v>
+        <v>0.9898041675400044</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.485774806240902</v>
+        <v>0.9898041952152813</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.485774861591456</v>
+        <v>0.9898042505658353</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.485775124506587</v>
+        <v>0.989804513480966</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.485775041480756</v>
+        <v>0.9898044304551352</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.485774833916179</v>
+        <v>0.9898042228905585</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.485774847753818</v>
+        <v>0.9898042367281967</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.485774986130202</v>
+        <v>0.9898043751045815</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.485774702458614</v>
+        <v>0.9898040914329929</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.485774529488133</v>
+        <v>0.989803918462512</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.485774425705845</v>
+        <v>0.9898038146802236</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.485774571001048</v>
+        <v>0.9898039599754275</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.485774813159721</v>
+        <v>0.9898042021341007</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.485774640189241</v>
+        <v>0.9898040291636198</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.485774342680014</v>
+        <v>0.9898037316543928</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.485774328842375</v>
+        <v>0.9898037178167542</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.485773962144955</v>
+        <v>0.989803351119335</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.485773962144955</v>
+        <v>0.989803351119335</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.986393030374176</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.485773899875583</v>
+        <v>0.9898032888499619</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.485773796093294</v>
+        <v>0.9898031850676734</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.485773623122813</v>
+        <v>0.9898030120971927</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.462243845257878</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.485773671554548</v>
+        <v>0.9898030605289273</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.485773311775948</v>
+        <v>0.9898027007503272</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.485773270263033</v>
+        <v>0.9898026592374118</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.485773325613586</v>
+        <v>0.9898027145879655</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.48577338096414</v>
+        <v>0.9898027699385195</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.485773422477056</v>
+        <v>0.9898028114514349</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.485773152643105</v>
+        <v>0.9898025416174847</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.485773207993659</v>
+        <v>0.9898025969680387</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.485773353288863</v>
+        <v>0.9898027422632426</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.485773318694767</v>
+        <v>0.9898027076691464</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.485773304857129</v>
+        <v>0.9898026938315078</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.485773394801779</v>
+        <v>0.989802783776158</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.986393030374176</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.485773713067463</v>
+        <v>0.9898031020418426</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.1058502080323613</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.485773533178163</v>
+        <v>0.9898029221525425</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8622438452578782</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.485773574691079</v>
+        <v>0.9898029636654579</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.462243845257878</v>
+        <v>0.7569672081768308</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.48577338788296</v>
+        <v>0.9898027768573386</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.485773457071152</v>
+        <v>0.9898028460455311</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.485773256425394</v>
+        <v>0.9898026453997733</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.48577329793831</v>
+        <v>0.9898026869126887</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.462243845257878</v>
+        <v>0.9569672081768309</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.485773325613586</v>
+        <v>0.9898027145879655</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000006.xlsx
+++ b/out/Attention-mamba2_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1378759145736694</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.114821583032608</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.127760112285614</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1312700659036636</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1286642849445343</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.127221405506134</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1060436218976974</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.1288511753082275</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.1350264698266983</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.1266719847917557</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1041248291730881</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.08926655352115631</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1096827238798141</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0970911830663681</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.09130224585533142</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.08934392035007477</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1019280552864075</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1177964806556702</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.125618115067482</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1276384443044662</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1139289885759354</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.09537141025066376</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.09766483306884766</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1211784780025482</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.1075026988983154</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.196383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.1097076088190079</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.05526821687817574</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.03404128924012184</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.02464349195361137</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.02982142940163612</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>-0.000177484005689621</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0008450672030448914</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.006509747356176376</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9569672081768309</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.06976430118083954</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9569672081768309</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02519845217466354</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0191507525742054</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.05503130331635475</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.007234644144773483</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01305681094527245</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.05521465465426445</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0497468002140522</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.05049263313412666</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.03937770053744316</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001868916883917991</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2405439506599493</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01369769498705864</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4815435480673604</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05555158254951009</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0112285353243351</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1848054764220475</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02909876778721809</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1848054764220475</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.02289506793022156</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1846764270315873</v>
+        <v>0.1805353231967278</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.3964676369177444</v>
+        <v>0.2282159622144663</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01950418762862682</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5452667921121083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9784011605977389</v>
+        <v>0.6374220041313774</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.07585961506419546</v>
+        <v>0.04366655291131923</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001742780208587646</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7330741868823708</v>
+        <v>0.4962059105595811</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1328753101658987</v>
+        <v>0.07648632621329152</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005557755008339882</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9230023779499026</v>
+        <v>0.6055332909506734</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.07276711699654888</v>
+        <v>0.04188645735538458</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0127355195581913</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9355472482495468</v>
+        <v>0.6127544298176431</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03005387904801072</v>
+        <v>0.01729971689228928</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1244550049304962</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9228115237015914</v>
+        <v>0.6054234131568402</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03744455424368934</v>
+        <v>0.02155396268611361</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.04564354568719864</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9676523856496301</v>
+        <v>0.6312351134164363</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.022546458456379</v>
+        <v>0.01297810855661497</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.04527445137500763</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9752755391208245</v>
+        <v>0.6356225115857507</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01714136955187149</v>
+        <v>0.009865561962379997</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0338268019258976</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9870028011655845</v>
+        <v>0.6423710901332695</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.007579101736862406</v>
+        <v>0.004360785304099126</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.08553647994995117</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.9850068797781947</v>
+        <v>0.641220136472065</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006012997386423449</v>
+        <v>0.0034579968195974</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.05997644737362862</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9894525224497505</v>
+        <v>0.6437766111456487</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.002979265954122921</v>
+        <v>0.001713516940890567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.06631682813167572</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9893942399526222</v>
+        <v>0.6437409398834182</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001731792845140836</v>
+        <v>0.0009928558557509325</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04619778320193291</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9898744806679504</v>
+        <v>0.6440151379854742</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0008619418221976032</v>
+        <v>0.000495382528248281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.06653256714344025</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9898684012668587</v>
+        <v>0.6440095149754481</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0004233225761948737</v>
+        <v>0.0002422197419648264</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.03516600653529167</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9898525241169843</v>
+        <v>0.6439982568560056</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002453239583427053</v>
+        <v>0.0001385190694498177</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.07829631865024567</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9899167479819124</v>
+        <v>0.6440329452052312</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>7.75828942169606e-05</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00255453959107399</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9898286182366882</v>
+        <v>0.643980284750449</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.767003179814982e-05</v>
+        <v>1.970370261998147e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01150093041360378</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9898240903899865</v>
+        <v>0.6439755581023584</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.701576517097656e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01099056005477905</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9898228750664795</v>
+        <v>0.6439727498763025</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.850902234816308e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002873986959457397</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9898170991236148</v>
+        <v>0.6439672843105835</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.184014912590811e-07</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.03235931694507599</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9898147902188129</v>
+        <v>0.6439638996921326</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.005904901772737503</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9898087906852162</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01020732522010803</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9898045480750622</v>
+        <v>0.6439586127969166</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.02537538856267929</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9898047763960969</v>
+        <v>0.6439588411179513</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002344183623790741</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9898048663407468</v>
+        <v>0.6439589310626013</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.02109574154019356</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.989804008407162</v>
+        <v>0.6439580731290164</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02570855058729649</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3452667921121083</v>
+        <v>0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9898042367281967</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02383546531200409</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5452667921121084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.989803441063985</v>
+        <v>0.6439575057858394</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.03305181488394737</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9898035033333581</v>
+        <v>0.6439575680552125</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01056864485144615</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9898035310086349</v>
+        <v>0.6439575957304894</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01144567131996155</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9898036832226582</v>
+        <v>0.6439577479445127</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02365579456090927</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3058502080323613</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9898033372816964</v>
+        <v>0.6439574020035509</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01583841443061829</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9898034133887081</v>
+        <v>0.6439574781105626</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.03149662539362907</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3058502080323614</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9898035794403698</v>
+        <v>0.6439576441622241</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002029582858085632</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3452667921121082</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9898039392189698</v>
+        <v>0.6439580039408241</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01876228116452694</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.196383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9898039599754275</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01345921866595745</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5452667921121084</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.989804063757716</v>
+        <v>0.6439581284795703</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.03202733770012856</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9898042920787506</v>
+        <v>0.6439583568006051</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.03265493363142014</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9898041675400044</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0387837253510952</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9898041952152813</v>
+        <v>0.6439582599371357</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001752626150846481</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9898042505658353</v>
+        <v>0.6439583152876897</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02779833972454071</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.989804513480966</v>
+        <v>0.6439585782028204</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02581256255507469</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9898044304551352</v>
+        <v>0.6439584951769896</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03462246432900429</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9898042228905585</v>
+        <v>0.6439582876124128</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.03123371675610542</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9898042367281967</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.02870987355709076</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9898043751045815</v>
+        <v>0.6439584398264359</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03028267621994019</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9898040914329929</v>
+        <v>0.6439581561548472</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03429994359612465</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.989803918462512</v>
+        <v>0.6439579831843665</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01525817811489105</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9898038146802236</v>
+        <v>0.6439578794020779</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03390390425920486</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9898039599754275</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.03171819821000099</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9898042021341007</v>
+        <v>0.6439582668559551</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02506571635603905</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9898040291636198</v>
+        <v>0.6439580938854741</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.03724702075123787</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9898037316543928</v>
+        <v>0.6439577963762472</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02069316431879997</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9898037178167542</v>
+        <v>0.6439577825386087</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.03596637025475502</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.989803351119335</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02414519712328911</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.989803351119335</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01438400615006685</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9898032888499619</v>
+        <v>0.6439573535718164</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0511455275118351</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9898031850676734</v>
+        <v>0.6439572497895278</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.02617022022604942</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9898030120971927</v>
+        <v>0.6439570768190471</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01951436325907707</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9898030605289273</v>
+        <v>0.6439571252507816</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.03405894711613655</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9898027007503272</v>
+        <v>0.6439567654721816</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.03301972895860672</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9898026592374118</v>
+        <v>0.6439567239592662</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0189041756093502</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9898027145879655</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.04035599902272224</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9898027699385195</v>
+        <v>0.6439568346603739</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03220506012439728</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9898028114514349</v>
+        <v>0.6439568761732892</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03305073082447052</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9898025416174847</v>
+        <v>0.6439566063393392</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0330486111342907</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9898025969680387</v>
+        <v>0.6439566616898931</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.03229929879307747</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7569672081768308</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9898027422632426</v>
+        <v>0.6439568069850971</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03351804614067078</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9898027076691464</v>
+        <v>0.6439567723910008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.02658175677061081</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9898026938315078</v>
+        <v>0.6439567585533622</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01246115565299988</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.989802783776158</v>
+        <v>0.6439568484980124</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.05403438210487366</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9898031020418426</v>
+        <v>0.6439571667636971</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01762297749519348</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1058502080323613</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9898029221525425</v>
+        <v>0.643956986874397</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.02298320457339287</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9898029636654579</v>
+        <v>0.6439570283873123</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02568849548697472</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7569672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9898027768573386</v>
+        <v>0.643956841579193</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.03427906706929207</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9898028460455311</v>
+        <v>0.6439569107673855</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0210082158446312</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9898026453997733</v>
+        <v>0.6439567101216277</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.03536302968859673</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9898026869126887</v>
+        <v>0.643956751634543</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.08091491460800171</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9569672081768309</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9898027145879655</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000006.xlsx
+++ b/out/Attention-mamba2_repeat_4_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1378759145736694</v>
+        <v>-0.1361141800880432</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.114821583032608</v>
+        <v>-0.1127950847148895</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.127760112285614</v>
+        <v>-0.1249598637223244</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1312700659036636</v>
+        <v>-0.1281485259532928</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1286642849445343</v>
+        <v>-0.1254190504550934</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.127221405506134</v>
+        <v>-0.1238815039396286</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1060436218976974</v>
+        <v>-0.1027410179376602</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.1288511753082275</v>
+        <v>-0.1255554556846619</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.1350264698266983</v>
+        <v>-0.1319833397865295</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.1266719847917557</v>
+        <v>-0.1233877763152122</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1041248291730881</v>
+        <v>-0.100683368742466</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.08926655352115631</v>
+        <v>-0.08582420647144318</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1096827238798141</v>
+        <v>-0.1060703620314598</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0970911830663681</v>
+        <v>-0.09357846528291702</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.09130224585533142</v>
+        <v>-0.08772338926792145</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.08934392035007477</v>
+        <v>-0.08581483364105225</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1019280552864075</v>
+        <v>-0.09836576133966446</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1177964806556702</v>
+        <v>-0.1143597587943077</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.02000000000000007</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.125618115067482</v>
+        <v>-0.1224136203527451</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1276384443044662</v>
+        <v>-0.124207466840744</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1139289885759354</v>
+        <v>-0.1102817431092262</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.09537141025066376</v>
+        <v>-0.09177248924970627</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.09766483306884766</v>
+        <v>-0.09405667334794998</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1211784780025482</v>
+        <v>-0.117646835744381</v>
       </c>
       <c r="JB25" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.1075026988983154</v>
+        <v>-0.1041027903556824</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.1097076088190079</v>
+        <v>-0.106898345053196</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.05526821687817574</v>
+        <v>0.05473093688488007</v>
       </c>
       <c r="JB28" t="n">
         <v>0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.03404128924012184</v>
+        <v>0.03380540758371353</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.02464349195361137</v>
+        <v>0.02480466663837433</v>
       </c>
       <c r="JB30" t="n">
         <v>0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.02982142940163612</v>
+        <v>0.03035640716552734</v>
       </c>
       <c r="JB31" t="n">
         <v>0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.000177484005689621</v>
+        <v>0.0002927929162979126</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0008450672030448914</v>
+        <v>0.00150635838508606</v>
       </c>
       <c r="JB33" t="n">
         <v>0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.006509747356176376</v>
+        <v>0.006966292858123779</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.06976430118083954</v>
+        <v>0.06976691633462906</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.02000000000000007</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.02519845217466354</v>
+        <v>0.02520756423473358</v>
       </c>
       <c r="JB36" t="n">
         <v>0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0191507525742054</v>
+        <v>0.0193907842040062</v>
       </c>
       <c r="JB37" t="n">
         <v>0.2599999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.05503130331635475</v>
+        <v>0.05530395358800888</v>
       </c>
       <c r="JB38" t="n">
         <v>0.1199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.007234644144773483</v>
+        <v>0.007324028760194778</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01305681094527245</v>
+        <v>0.01329328864812851</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.05521465465426445</v>
+        <v>0.05505974590778351</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0497468002140522</v>
+        <v>0.04886242747306824</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.05049263313412666</v>
+        <v>0.04921775311231613</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.03937770053744316</v>
+        <v>0.03812358528375626</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7199999999999999</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001826481971237809</v>
+        <v>-9.770429748657625e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2350824573080914</v>
+        <v>0.1257528312016157</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01369769498705864</v>
+        <v>0.01231054961681366</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.02000000000000007</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4706098037066381</v>
+        <v>0.2517440691349432</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05429020204081502</v>
+        <v>-0.02904159478076405</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0112285353243351</v>
+        <v>0.009928684681653976</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.02000000000000007</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1806096070701526</v>
+        <v>0.09661353212336497</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02909876778721809</v>
+        <v>0.02791114151477814</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1806096070701526</v>
+        <v>0.09661353212336497</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.02289506793022156</v>
+        <v>0.02150850743055344</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1805353231967278</v>
+        <v>0.09654453329845658</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2282159622144663</v>
+        <v>0.2119793124472731</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.01950418762862682</v>
+        <v>-0.02093514055013657</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6374220041313774</v>
+        <v>0.5209252585495711</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.04366655291131923</v>
+        <v>0.04055985292731279</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001742780208587646</v>
+        <v>-0.002958508208394051</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4962059105595811</v>
+        <v>0.3897563096354802</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.07648632621329152</v>
+        <v>0.07104442902114899</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.005557755008339882</v>
+        <v>-0.006961220875382423</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6055332909506734</v>
+        <v>0.4913051968784577</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04188645735538458</v>
+        <v>0.0389062764190868</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0127355195581913</v>
+        <v>-0.01419897004961967</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6127544298176431</v>
+        <v>0.4980125616515447</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01729971689228928</v>
+        <v>0.0160688587643669</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.1244550049304962</v>
+        <v>-0.130379319190979</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6054234131568402</v>
+        <v>0.491203133829799</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02155396268611361</v>
+        <v>0.02002090950393406</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.04564354568719864</v>
+        <v>-0.04682733118534088</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6312351134164363</v>
+        <v>0.5151783976026831</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01297810855661497</v>
+        <v>0.01205411957852316</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.04527445137500763</v>
+        <v>-0.04965925961732864</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6356225115857507</v>
+        <v>0.519253195174218</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.009865561962379997</v>
+        <v>0.009163088404445782</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0338268019258976</v>
+        <v>-0.03427644073963165</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6423710901332695</v>
+        <v>0.5255211313460395</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004360785304099126</v>
+        <v>0.004049284059248951</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.08553647994995117</v>
+        <v>0.08484680205583572</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.641220136472065</v>
+        <v>0.5244517345605919</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0034579968195974</v>
+        <v>0.003213342273711786</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.05997644737362862</v>
+        <v>0.05943295359611511</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6437766111456487</v>
+        <v>0.5268263775669222</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001713516940890567</v>
+        <v>0.00159094440798862</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.06631682813167572</v>
+        <v>0.06275813281536102</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6437409398834182</v>
+        <v>0.5267928939201929</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0009928558557509325</v>
+        <v>0.0009230350378558236</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.04619778320193291</v>
+        <v>0.04593890905380249</v>
       </c>
       <c r="JB60" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6440151379854742</v>
+        <v>0.5270471766474789</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.000495382528248281</v>
+        <v>0.0004575629185550971</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.06653256714344025</v>
+        <v>-0.07051387429237366</v>
       </c>
       <c r="JB61" t="n">
         <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6440095149754481</v>
+        <v>0.5270416007254198</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002422197419648264</v>
+        <v>0.0002249718529905362</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.03516600653529167</v>
+        <v>-0.03862930834293365</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6439982568560056</v>
+        <v>0.5270307792189617</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001385190694498177</v>
+        <v>0.0001285061111161094</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.07829631865024567</v>
+        <v>-0.08178128302097321</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6440329452052312</v>
+        <v>0.5270626986135903</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.187137239341006e-05</v>
+        <v>3.963940227943816e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.00255453959107399</v>
+        <v>-0.005194146186113358</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.643980284750449</v>
+        <v>0.5270133620005378</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.01150093041360378</v>
+        <v>-0.01374835520982742</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6439755581023584</v>
+        <v>0.5270086105022738</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.01099056005477905</v>
+        <v>0.009130973368883133</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6439727498763025</v>
+        <v>0.52700560163046</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002873986959457397</v>
+        <v>-0.005187321454286575</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6439672843105835</v>
+        <v>0.5270002151463025</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.03235931694507599</v>
+        <v>-0.03513918817043304</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6439638996921326</v>
+        <v>0.5269968305278516</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.005904901772737503</v>
+        <v>0.003557752817869186</v>
       </c>
       <c r="JB69" t="n">
         <v>0.1600000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6439582322618589</v>
+        <v>0.5269911630975779</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.01020732522010803</v>
+        <v>-0.01225167885422707</v>
       </c>
       <c r="JB70" t="n">
         <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6439586127969166</v>
+        <v>0.5269915436326356</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.02537538856267929</v>
+        <v>0.02381205558776855</v>
       </c>
       <c r="JB71" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6439588411179513</v>
+        <v>0.5269917719536703</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002344183623790741</v>
+        <v>-0.003992766141891479</v>
       </c>
       <c r="JB72" t="n">
         <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6439589310626013</v>
+        <v>0.5269918618983203</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.02109574154019356</v>
+        <v>0.01941012591123581</v>
       </c>
       <c r="JB73" t="n">
         <v>0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6439580731290164</v>
+        <v>0.5269910039647354</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.02570855058729649</v>
+        <v>-0.0283405426889658</v>
       </c>
       <c r="JB74" t="n">
         <v>0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6439583014500512</v>
+        <v>0.5269912322857702</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.02383546531200409</v>
+        <v>-0.02631122060120106</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6439575057858394</v>
+        <v>0.5269904366215584</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.03305181488394737</v>
+        <v>0.0316738486289978</v>
       </c>
       <c r="JB76" t="n">
         <v>0.1600000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6439575680552125</v>
+        <v>0.5269904988909315</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.01056864485144615</v>
+        <v>0.009024400264024734</v>
       </c>
       <c r="JB77" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6439575957304894</v>
+        <v>0.5269905265662084</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.01144567131996155</v>
+        <v>-0.01334780361503363</v>
       </c>
       <c r="JB78" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6439577479445127</v>
+        <v>0.5269906787802316</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.02365579456090927</v>
+        <v>0.02235325425863266</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6439574020035509</v>
+        <v>0.5269903328392699</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.01583841443061829</v>
+        <v>0.01484298333525658</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6439574781105626</v>
+        <v>0.5269904089462816</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.03149662539362907</v>
+        <v>0.03071551769971848</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6439576441622241</v>
+        <v>0.5269905749979431</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002029582858085632</v>
+        <v>-0.003831584006547928</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6439580039408241</v>
+        <v>0.5269909347765431</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.01876228116452694</v>
+        <v>-0.0213631559163332</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6439580246972819</v>
+        <v>0.5269909555330009</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.01345921866595745</v>
+        <v>-0.01572655886411667</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6439581284795703</v>
+        <v>0.5269910593152893</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.03202733770012856</v>
+        <v>0.03089030832052231</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6439583568006051</v>
+        <v>0.5269912876363241</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.03265493363142014</v>
+        <v>0.03203389048576355</v>
       </c>
       <c r="JB86" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6439582322618589</v>
+        <v>0.5269911630975779</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0387837253510952</v>
+        <v>0.03832851350307465</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6439582599371357</v>
+        <v>0.5269911907728547</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.001752626150846481</v>
+        <v>0.0006521493196487427</v>
       </c>
       <c r="JB88" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6439583152876897</v>
+        <v>0.5269912461234086</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.02779833972454071</v>
+        <v>0.02692433074116707</v>
       </c>
       <c r="JB89" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6439585782028204</v>
+        <v>0.5269915090385394</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.02581256255507469</v>
+        <v>0.02512401342391968</v>
       </c>
       <c r="JB90" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6439584951769896</v>
+        <v>0.5269914260127085</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.03462246432900429</v>
+        <v>0.03417133539915085</v>
       </c>
       <c r="JB91" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6439582876124128</v>
+        <v>0.5269912184481318</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.03123371675610542</v>
+        <v>0.03083816170692444</v>
       </c>
       <c r="JB92" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6439583014500512</v>
+        <v>0.5269912322857702</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.02870987355709076</v>
+        <v>0.02829796448349953</v>
       </c>
       <c r="JB93" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6439584398264359</v>
+        <v>0.5269913706621548</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.03028267621994019</v>
+        <v>0.02990258112549782</v>
       </c>
       <c r="JB94" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6439581561548472</v>
+        <v>0.5269910869905662</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.03429994359612465</v>
+        <v>0.03402180969715118</v>
       </c>
       <c r="JB95" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6439579831843665</v>
+        <v>0.5269909140200855</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.01525817811489105</v>
+        <v>0.01462622731924057</v>
       </c>
       <c r="JB96" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6439578794020779</v>
+        <v>0.5269908102377969</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.03390390425920486</v>
+        <v>0.0335002988576889</v>
       </c>
       <c r="JB97" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6439580246972819</v>
+        <v>0.5269909555330009</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.03171819821000099</v>
+        <v>0.03141768649220467</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6439582668559551</v>
+        <v>0.5269911976916741</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.02506571635603905</v>
+        <v>0.02464443072676659</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6439580938854741</v>
+        <v>0.5269910247211931</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.03724702075123787</v>
+        <v>0.03706327825784683</v>
       </c>
       <c r="JB100" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6439577963762472</v>
+        <v>0.5269907272119662</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.02069316431879997</v>
+        <v>0.02023783326148987</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6439577825386087</v>
+        <v>0.5269907133743277</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.03596637025475502</v>
+        <v>0.03575725108385086</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6439574158411895</v>
+        <v>0.5269903466769085</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.02414519712328911</v>
+        <v>0.02354159206151962</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6439574158411895</v>
+        <v>0.5269903466769085</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.01438400615006685</v>
+        <v>-0.01574159227311611</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6439573535718164</v>
+        <v>0.5269902844075354</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0511455275118351</v>
+        <v>0.05078284442424774</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6439572497895278</v>
+        <v>0.5269901806252468</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.02617022022604942</v>
+        <v>0.02581070363521576</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6439570768190471</v>
+        <v>0.5269900076547661</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.01951436325907707</v>
+        <v>0.01891375705599785</v>
       </c>
       <c r="JB107" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6439571252507816</v>
+        <v>0.5269900560865006</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.03405894711613655</v>
+        <v>0.03372461348772049</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6439567654721816</v>
+        <v>0.5269896963079006</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.03301972895860672</v>
+        <v>0.0329105518758297</v>
       </c>
       <c r="JB109" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6439567239592662</v>
+        <v>0.5269896547949852</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0189041756093502</v>
+        <v>0.0183865875005722</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6439567793098199</v>
+        <v>0.5269897101455389</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.04035599902272224</v>
+        <v>0.04029534012079239</v>
       </c>
       <c r="JB111" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6439568346603739</v>
+        <v>0.5269897654960929</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.03220506012439728</v>
+        <v>0.03205648809671402</v>
       </c>
       <c r="JB112" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6439568761732892</v>
+        <v>0.5269898070090082</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.03305073082447052</v>
+        <v>0.03300747275352478</v>
       </c>
       <c r="JB113" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6439566063393392</v>
+        <v>0.5269895371750581</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0330486111342907</v>
+        <v>0.03300582244992256</v>
       </c>
       <c r="JB114" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6439566616898931</v>
+        <v>0.5269895925256121</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.03229929879307747</v>
+        <v>0.03222860023379326</v>
       </c>
       <c r="JB115" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6439568069850971</v>
+        <v>0.526989737820816</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.03351804614067078</v>
+        <v>0.03345648944377899</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6439567723910008</v>
+        <v>0.5269897032267198</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.02658175677061081</v>
+        <v>0.02653099969029427</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6439567585533622</v>
+        <v>0.5269896893890812</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.01246115565299988</v>
+        <v>0.01111374050378799</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6439568484980124</v>
+        <v>0.5269897793337314</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.05403438210487366</v>
+        <v>-0.0572010762989521</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6439571667636971</v>
+        <v>0.5269900975994161</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.01762297749519348</v>
+        <v>0.01569397002458572</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.643956986874397</v>
+        <v>0.5269899177101159</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.02298320457339287</v>
+        <v>0.02190699800848961</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6439570283873123</v>
+        <v>0.5269899592230313</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.02568849548697472</v>
+        <v>0.02498763799667358</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.643956841579193</v>
+        <v>0.526989772414912</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.03427906706929207</v>
+        <v>0.03390339389443398</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6439569107673855</v>
+        <v>0.5269898416031045</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0210082158446312</v>
+        <v>0.02048354223370552</v>
       </c>
       <c r="JB124" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6439567101216277</v>
+        <v>0.5269896409573467</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.03536302968859673</v>
+        <v>0.03518413752317429</v>
       </c>
       <c r="JB125" t="n">
         <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.643956751634543</v>
+        <v>0.526989682470262</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.08091491460800171</v>
+        <v>0.08025181293487549</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6439567793098199</v>
+        <v>0.5269897101455389</v>
       </c>
     </row>
   </sheetData>
